--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:31</t>
+    <t xml:space="preserve">2026-09-24 01:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -786,7 +786,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G13" s="2"/>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="G30" s="2"/>
     </row>
@@ -1451,13 +1451,13 @@
         <v>21</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.62</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="48">
@@ -1821,10 +1821,10 @@
         <v>-0.74</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-0.81</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="65">
@@ -2119,10 +2119,10 @@
         <v>0.49</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="79">
@@ -2142,10 +2142,10 @@
         <v>0.23</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.15</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.24</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="80">
@@ -2165,10 +2165,10 @@
         <v>0.53</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="81">
@@ -2188,10 +2188,10 @@
         <v>0.42</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="82">
@@ -2234,10 +2234,10 @@
         <v>-0.71</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.72</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.58</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="84">
@@ -2257,10 +2257,10 @@
         <v>0.4</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>0.6</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="85">
@@ -2280,10 +2280,10 @@
         <v>-0.06</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="86">
@@ -2486,10 +2486,10 @@
         <v>0.61</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="96">
@@ -2509,10 +2509,10 @@
         <v>0.75</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.72</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="97">
@@ -2532,10 +2532,10 @@
         <v>0.39</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="98">
@@ -2555,10 +2555,10 @@
         <v>0.01</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="99">
@@ -2601,10 +2601,10 @@
         <v>0.52</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.41</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="101">
@@ -2624,10 +2624,10 @@
         <v>0.66</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.66</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="102">
@@ -2650,7 +2650,7 @@
         <v>-0.03</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="103">
@@ -2853,10 +2853,10 @@
         <v>-0.38</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="113">
@@ -2876,10 +2876,10 @@
         <v>-0.6</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="114">
@@ -2899,10 +2899,10 @@
         <v>-0.15</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="115">
@@ -2919,13 +2919,13 @@
         <v>21</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="F115" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G115" s="2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="116">
@@ -2968,10 +2968,10 @@
         <v>-0.37</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.2</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="118">
@@ -2991,10 +2991,10 @@
         <v>0.28</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.24</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="119">
@@ -3220,10 +3220,10 @@
         <v>-0.57</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="130">
@@ -3243,10 +3243,10 @@
         <v>-0.6</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="131">
@@ -3289,10 +3289,10 @@
         <v>-0.05</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="133">
@@ -3335,10 +3335,10 @@
         <v>-0.28</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="135">
@@ -3358,10 +3358,10 @@
         <v>-0.23</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="136">
@@ -3381,10 +3381,10 @@
         <v>-0.67</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="137">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_tarapaca.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:21</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2021_tarapaca.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
